--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table133.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table133.xlsx
@@ -295,8 +295,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="#0.000"/>
-    <numFmt numFmtId="169" formatCode="#0.0"/>
+    <numFmt numFmtId="164" formatCode="#0.000"/>
+    <numFmt numFmtId="165" formatCode="#0.0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -371,7 +371,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -386,20 +386,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -816,47 +816,47 @@
       <c r="C4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="15"/>
-      <c r="AA4" s="15"/>
-      <c r="AB4" s="15"/>
-      <c r="AC4" s="15"/>
-      <c r="AD4" s="15" t="s">
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="15"/>
-      <c r="AF4" s="15"/>
-      <c r="AG4" s="15"/>
-      <c r="AH4" s="15" t="s">
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="AI4" s="15"/>
-      <c r="AJ4" s="15"/>
+      <c r="AI4" s="17"/>
+      <c r="AJ4" s="17"/>
     </row>
     <row r="5" spans="1:36" ht="63" customHeight="1">
       <c r="A5" s="4"/>
@@ -5120,7 +5120,7 @@
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="15" t="s">
         <v>64</v>
       </c>
       <c r="C47" s="4"/>
@@ -5162,7 +5162,7 @@
       <c r="A48" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="15" t="s">
         <v>65</v>
       </c>
       <c r="C48" s="4"/>
@@ -5204,7 +5204,7 @@
       <c r="A49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="15" t="s">
         <v>66</v>
       </c>
       <c r="C49" s="4"/>
